--- a/planilhas_competidores/Bruno_previsoes.xlsx
+++ b/planilhas_competidores/Bruno_previsoes.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BIEL\bolao-copa-2026\planilhas_competidores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8414870-EFBF-4670-9FE1-0AA885691133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6605188-3911-4960-BF53-A977CCC40A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="0" windowWidth="10455" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -373,14 +386,25 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -400,17 +424,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{580901FF-E7FD-4063-9719-2B2C8E0A9D74}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{21C0E4F6-8007-4344-ACE5-25F6ED197B3D}"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{36AFFA3E-DD00-4408-BCCD-D903AE251DE6}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -819,6 +851,12 @@
       <c r="G4" t="s">
         <v>21</v>
       </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -842,6 +880,12 @@
       <c r="G5" t="s">
         <v>18</v>
       </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -865,6 +909,12 @@
       <c r="G6" t="s">
         <v>14</v>
       </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -888,6 +938,12 @@
       <c r="G7" t="s">
         <v>24</v>
       </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -969,6 +1025,12 @@
       <c r="G10" t="s">
         <v>34</v>
       </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -992,6 +1054,12 @@
       <c r="G11" t="s">
         <v>36</v>
       </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -1015,6 +1083,12 @@
       <c r="G12" t="s">
         <v>36</v>
       </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -1038,6 +1112,12 @@
       <c r="G13" t="s">
         <v>37</v>
       </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -1119,6 +1199,12 @@
       <c r="G16" t="s">
         <v>44</v>
       </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -1142,6 +1228,12 @@
       <c r="G17" t="s">
         <v>46</v>
       </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
@@ -1165,6 +1257,12 @@
       <c r="G18" t="s">
         <v>21</v>
       </c>
+      <c r="H18">
+        <v>3</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -1188,6 +1286,12 @@
       <c r="G19" t="s">
         <v>47</v>
       </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>2</v>
+      </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -1269,6 +1373,12 @@
       <c r="G22" t="s">
         <v>37</v>
       </c>
+      <c r="H22">
+        <v>4</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
@@ -1292,6 +1402,12 @@
       <c r="G23" t="s">
         <v>56</v>
       </c>
+      <c r="H23">
+        <v>3</v>
+      </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
@@ -1315,6 +1431,12 @@
       <c r="G24" t="s">
         <v>34</v>
       </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
@@ -1338,6 +1460,12 @@
       <c r="G25" t="s">
         <v>56</v>
       </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>3</v>
+      </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
@@ -1419,6 +1547,12 @@
       <c r="G28" t="s">
         <v>29</v>
       </c>
+      <c r="H28">
+        <v>4</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
@@ -1442,6 +1576,12 @@
       <c r="G29" t="s">
         <v>68</v>
       </c>
+      <c r="H29">
+        <v>2</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -1465,6 +1605,12 @@
       <c r="G30" t="s">
         <v>46</v>
       </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
@@ -1488,6 +1634,12 @@
       <c r="G31" t="s">
         <v>41</v>
       </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>3</v>
+      </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
@@ -1869,6 +2021,12 @@
       <c r="G46" t="s">
         <v>21</v>
       </c>
+      <c r="H46">
+        <v>5</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
@@ -1892,6 +2050,12 @@
       <c r="G47" t="s">
         <v>47</v>
       </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>2</v>
+      </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -1915,8 +2079,14 @@
       <c r="G48" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H48">
+        <v>2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>84</v>
       </c>
@@ -1938,8 +2108,14 @@
       <c r="G49" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>90</v>
       </c>
@@ -1961,8 +2137,14 @@
       <c r="G50" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H50">
+        <v>3</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>90</v>
       </c>
@@ -1984,8 +2166,14 @@
       <c r="G51" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>90</v>
       </c>
@@ -2007,8 +2195,14 @@
       <c r="G52" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H52">
+        <v>4</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>90</v>
       </c>
@@ -2030,8 +2224,14 @@
       <c r="G53" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H53">
+        <v>1</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>90</v>
       </c>
@@ -2053,8 +2253,14 @@
       <c r="G54" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>90</v>
       </c>
@@ -2076,8 +2282,14 @@
       <c r="G55" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H55">
+        <v>1</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>98</v>
       </c>
@@ -2099,8 +2311,14 @@
       <c r="G56" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H56">
+        <v>4</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>98</v>
       </c>
@@ -2122,8 +2340,14 @@
       <c r="G57" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H57">
+        <v>1</v>
+      </c>
+      <c r="I57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>98</v>
       </c>
@@ -2145,8 +2369,14 @@
       <c r="G58" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H58">
+        <v>3</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>98</v>
       </c>
@@ -2168,8 +2398,14 @@
       <c r="G59" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H59">
+        <v>2</v>
+      </c>
+      <c r="I59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>98</v>
       </c>
@@ -2191,8 +2427,14 @@
       <c r="G60" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H60">
+        <v>3</v>
+      </c>
+      <c r="I60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>98</v>
       </c>
@@ -2214,8 +2456,14 @@
       <c r="G61" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>105</v>
       </c>
@@ -2237,8 +2485,14 @@
       <c r="G62" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H62">
+        <v>5</v>
+      </c>
+      <c r="I62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>105</v>
       </c>
@@ -2260,8 +2514,14 @@
       <c r="G63" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H63">
+        <v>2</v>
+      </c>
+      <c r="I63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>105</v>
       </c>
@@ -2283,8 +2543,14 @@
       <c r="G64" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H64">
+        <v>6</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>105</v>
       </c>
@@ -2306,8 +2572,14 @@
       <c r="G65" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H65">
+        <v>2</v>
+      </c>
+      <c r="I65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>105</v>
       </c>
@@ -2329,8 +2601,14 @@
       <c r="G66" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H66">
+        <v>1</v>
+      </c>
+      <c r="I66">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>105</v>
       </c>
@@ -2352,8 +2630,14 @@
       <c r="G67" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H67">
+        <v>1</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>111</v>
       </c>
@@ -2375,8 +2659,14 @@
       <c r="G68" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H68">
+        <v>2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>111</v>
       </c>
@@ -2398,8 +2688,14 @@
       <c r="G69" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>111</v>
       </c>
@@ -2421,8 +2717,14 @@
       <c r="G70" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H70">
+        <v>3</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>111</v>
       </c>
@@ -2444,8 +2746,14 @@
       <c r="G71" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H71">
+        <v>1</v>
+      </c>
+      <c r="I71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>111</v>
       </c>
@@ -2467,8 +2775,14 @@
       <c r="G72" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H72">
+        <v>2</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>111</v>
       </c>
@@ -2489,6 +2803,12 @@
       </c>
       <c r="G73" t="s">
         <v>41</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/planilhas_competidores/Bruno_previsoes.xlsx
+++ b/planilhas_competidores/Bruno_previsoes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BIEL\bolao-copa-2026\planilhas_competidores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6605188-3911-4960-BF53-A977CCC40A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35EDBEDC-C4C9-4355-B0E3-C04A09E902DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10035" yWindow="0" windowWidth="10455" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -855,7 +855,7 @@
         <v>2</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -1026,10 +1026,10 @@
         <v>34</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1055,7 +1055,7 @@
         <v>36</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11">
         <v>1</v>
@@ -1200,7 +1200,7 @@
         <v>44</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16">
         <v>2</v>
@@ -1229,7 +1229,7 @@
         <v>46</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1374,10 +1374,10 @@
         <v>37</v>
       </c>
       <c r="H22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -1403,10 +1403,10 @@
         <v>56</v>
       </c>
       <c r="H23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -2170,7 +2170,7 @@
         <v>1</v>
       </c>
       <c r="I51">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -2315,7 +2315,7 @@
         <v>4</v>
       </c>
       <c r="I56">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
@@ -2344,7 +2344,7 @@
         <v>1</v>
       </c>
       <c r="I57">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -2486,10 +2486,10 @@
         <v>62</v>
       </c>
       <c r="H62">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I62">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
@@ -2515,10 +2515,10 @@
         <v>14</v>
       </c>
       <c r="H63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -2663,7 +2663,7 @@
         <v>2</v>
       </c>
       <c r="I68">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
@@ -2689,7 +2689,7 @@
         <v>29</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69">
         <v>1</v>

--- a/planilhas_competidores/Bruno_previsoes.xlsx
+++ b/planilhas_competidores/Bruno_previsoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BIEL\bolao-copa-2026\planilhas_competidores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35EDBEDC-C4C9-4355-B0E3-C04A09E902DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACCF80C4-CA4D-496C-A6D9-9F4172897094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10035" yWindow="0" windowWidth="10455" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1548,7 +1548,7 @@
         <v>29</v>
       </c>
       <c r="H28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I28">
         <v>1</v>
@@ -1721,6 +1721,12 @@
       <c r="G34" t="s">
         <v>62</v>
       </c>
+      <c r="H34">
+        <v>2</v>
+      </c>
+      <c r="I34">
+        <v>2</v>
+      </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
@@ -1743,6 +1749,12 @@
       </c>
       <c r="G35" t="s">
         <v>24</v>
+      </c>
+      <c r="H35">
+        <v>2</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">

--- a/planilhas_competidores/Bruno_previsoes.xlsx
+++ b/planilhas_competidores/Bruno_previsoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BIEL\bolao-copa-2026\planilhas_competidores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACCF80C4-CA4D-496C-A6D9-9F4172897094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB61DC4-C25F-4EFC-81C2-F09B83339B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10035" yWindow="0" windowWidth="10455" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1883,6 +1883,12 @@
       <c r="G40" t="s">
         <v>34</v>
       </c>
+      <c r="H40">
+        <v>2</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
@@ -1906,6 +1912,12 @@
       <c r="G41" t="s">
         <v>36</v>
       </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
@@ -2034,7 +2046,7 @@
         <v>21</v>
       </c>
       <c r="H46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -2063,7 +2075,7 @@
         <v>47</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47">
         <v>2</v>

--- a/planilhas_competidores/Bruno_previsoes.xlsx
+++ b/planilhas_competidores/Bruno_previsoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BIEL\bolao-copa-2026\planilhas_competidores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB61DC4-C25F-4EFC-81C2-F09B83339B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C9CBBE-58C3-4DFC-B416-85526375C05E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10035" yWindow="0" windowWidth="10455" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2568,7 +2568,7 @@
         <v>62</v>
       </c>
       <c r="H64">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I64">
         <v>1</v>
@@ -2597,10 +2597,10 @@
         <v>18</v>
       </c>
       <c r="H65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I65">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -2771,10 +2771,10 @@
         <v>29</v>
       </c>
       <c r="H71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I71">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">

--- a/planilhas_competidores/Bruno_previsoes.xlsx
+++ b/planilhas_competidores/Bruno_previsoes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BIEL\bolao-copa-2026\planilhas_competidores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C9CBBE-58C3-4DFC-B416-85526375C05E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF32DFB-DC08-4A22-B1C2-6A47AFA81992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10035" yWindow="0" windowWidth="10455" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2220,7 +2220,7 @@
         <v>46</v>
       </c>
       <c r="H52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2249,7 +2249,7 @@
         <v>41</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I53">
         <v>1</v>
